--- a/research/traditional_assets/database/data/ireland/ireland_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_software_system_application.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.176</v>
+        <v>0.1415</v>
       </c>
       <c r="G2">
-        <v>-0.04301724137931034</v>
+        <v>-0.4742230945371279</v>
       </c>
       <c r="H2">
-        <v>-0.07198275862068966</v>
+        <v>-0.5498855086686293</v>
       </c>
       <c r="I2">
-        <v>-0.2603448275862069</v>
+        <v>-0.5714753025842328</v>
       </c>
       <c r="J2">
-        <v>-0.2603448275862069</v>
+        <v>-0.5714753025842328</v>
       </c>
       <c r="K2">
-        <v>-4.18</v>
+        <v>-20.39</v>
       </c>
       <c r="L2">
-        <v>-0.1801724137931034</v>
+        <v>-0.666993784756297</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.000392349190779794</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,67 +627,73 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.008</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>2.73</v>
+        <v>13.17</v>
       </c>
       <c r="V2">
-        <v>0.03573298429319371</v>
+        <v>0.12861328125</v>
       </c>
       <c r="W2">
-        <v>0.1553903345724907</v>
+        <v>3.339351517260455</v>
       </c>
       <c r="X2">
-        <v>0.1342721398162007</v>
+        <v>0.113308265739807</v>
       </c>
       <c r="Y2">
-        <v>0.02111819475629004</v>
+        <v>3.226043251520648</v>
+      </c>
+      <c r="Z2">
+        <v>37.14459295261241</v>
       </c>
       <c r="AB2">
-        <v>0.132977025426992</v>
+        <v>0.1086596714406361</v>
       </c>
       <c r="AD2">
-        <v>1.28</v>
+        <v>12.837</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.28</v>
+        <v>12.837</v>
       </c>
       <c r="AG2">
-        <v>-1.45</v>
+        <v>-0.3330000000000002</v>
       </c>
       <c r="AH2">
-        <v>0.0164778578784758</v>
+        <v>0.1113965132726468</v>
       </c>
       <c r="AI2">
-        <v>-2.098360655737705</v>
+        <v>1.389736927573888</v>
       </c>
       <c r="AJ2">
-        <v>-0.01934623082054703</v>
+        <v>-0.003262562826378753</v>
       </c>
       <c r="AK2">
-        <v>0.4341317365269461</v>
+        <v>0.08466819221967968</v>
       </c>
       <c r="AL2">
-        <v>1.77</v>
+        <v>0.845</v>
       </c>
       <c r="AM2">
-        <v>1.77</v>
+        <v>0.845</v>
       </c>
       <c r="AN2">
-        <v>-0.2210708117443869</v>
+        <v>-0.7467713787085515</v>
       </c>
       <c r="AO2">
-        <v>-3.412429378531074</v>
+        <v>-20.67455621301775</v>
       </c>
       <c r="AP2">
-        <v>0.2504317789291882</v>
+        <v>0.01937172774869111</v>
       </c>
       <c r="AQ2">
-        <v>-3.412429378531074</v>
+        <v>-20.67455621301775</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Datalex plc (ISE:DLE)</t>
+          <t>ENGAGE XR Holdings plc (AIM:EXR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -707,25 +713,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.176</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G3">
-        <v>-0.04301724137931034</v>
+        <v>-1.334135667396061</v>
       </c>
       <c r="H3">
-        <v>-0.07198275862068966</v>
+        <v>-1.380743982494529</v>
       </c>
       <c r="I3">
-        <v>-0.2603448275862069</v>
+        <v>-1.284463894967177</v>
       </c>
       <c r="J3">
-        <v>-0.2603448275862069</v>
+        <v>-1.284463894967177</v>
       </c>
       <c r="K3">
-        <v>-4.18</v>
+        <v>-5.89</v>
       </c>
       <c r="L3">
-        <v>-0.1801724137931034</v>
+        <v>-1.288840262582057</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,64 +755,195 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.73</v>
+        <v>10.3</v>
       </c>
       <c r="V3">
-        <v>0.03573298429319371</v>
+        <v>0.7518248175182483</v>
       </c>
       <c r="W3">
-        <v>0.1553903345724907</v>
+        <v>-0.9932546374367622</v>
       </c>
       <c r="X3">
-        <v>0.1342721398162007</v>
+        <v>0.1089712255486277</v>
       </c>
       <c r="Y3">
-        <v>0.02111819475629004</v>
+        <v>-1.10222586298539</v>
+      </c>
+      <c r="Z3">
+        <v>5.552855407047391</v>
+      </c>
+      <c r="AA3">
+        <v>-7.132442284325642</v>
       </c>
       <c r="AB3">
-        <v>0.132977025426992</v>
+        <v>0.1088192507299333</v>
+      </c>
+      <c r="AC3">
+        <v>-7.241261535055576</v>
       </c>
       <c r="AD3">
-        <v>1.28</v>
+        <v>0.037</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.28</v>
+        <v>0.037</v>
       </c>
       <c r="AG3">
-        <v>-1.45</v>
+        <v>-10.263</v>
       </c>
       <c r="AH3">
-        <v>0.0164778578784758</v>
+        <v>0.00269345563077819</v>
       </c>
       <c r="AI3">
-        <v>-2.098360655737705</v>
+        <v>0.003263649995589661</v>
       </c>
       <c r="AJ3">
-        <v>-0.01934623082054703</v>
+        <v>-2.986034332266512</v>
       </c>
       <c r="AK3">
-        <v>0.4341317365269461</v>
+        <v>-9.896817743490832</v>
       </c>
       <c r="AL3">
-        <v>1.77</v>
+        <v>0.015</v>
       </c>
       <c r="AM3">
-        <v>1.77</v>
+        <v>0.015</v>
       </c>
       <c r="AN3">
-        <v>-0.2210708117443869</v>
+        <v>-0.006390328151986183</v>
       </c>
       <c r="AO3">
-        <v>-3.412429378531074</v>
+        <v>-391.3333333333334</v>
       </c>
       <c r="AP3">
-        <v>0.2504317789291882</v>
+        <v>1.772538860103627</v>
       </c>
       <c r="AQ3">
-        <v>-3.412429378531074</v>
+        <v>-391.3333333333334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Datalex plc (ISE:DLE)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Software (System &amp; Application)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.149</v>
+      </c>
+      <c r="G4">
+        <v>-0.3230769230769231</v>
+      </c>
+      <c r="H4">
+        <v>-0.4038461538461539</v>
+      </c>
+      <c r="I4">
+        <v>-0.4461538461538461</v>
+      </c>
+      <c r="J4">
+        <v>-0.4461538461538461</v>
+      </c>
+      <c r="K4">
+        <v>-14.5</v>
+      </c>
+      <c r="L4">
+        <v>-0.5576923076923077</v>
+      </c>
+      <c r="M4">
+        <v>0.008</v>
+      </c>
+      <c r="N4">
+        <v>9.019165727170236e-05</v>
+      </c>
+      <c r="O4">
+        <v>-0.0005517241379310345</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0.008</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>2.87</v>
+      </c>
+      <c r="V4">
+        <v>0.03235625704622323</v>
+      </c>
+      <c r="W4">
+        <v>7.671957671957673</v>
+      </c>
+      <c r="X4">
+        <v>0.1176453059309863</v>
+      </c>
+      <c r="Y4">
+        <v>7.554312366026686</v>
+      </c>
+      <c r="AB4">
+        <v>0.108500092151339</v>
+      </c>
+      <c r="AD4">
+        <v>12.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>12.8</v>
+      </c>
+      <c r="AG4">
+        <v>9.93</v>
+      </c>
+      <c r="AH4">
+        <v>0.1261083743842365</v>
+      </c>
+      <c r="AI4">
+        <v>-6.095238095238097</v>
+      </c>
+      <c r="AJ4">
+        <v>0.1006793064990368</v>
+      </c>
+      <c r="AK4">
+        <v>-1.997987927565392</v>
+      </c>
+      <c r="AL4">
+        <v>0.83</v>
+      </c>
+      <c r="AM4">
+        <v>0.83</v>
+      </c>
+      <c r="AN4">
+        <v>-1.12280701754386</v>
+      </c>
+      <c r="AO4">
+        <v>-13.97590361445783</v>
+      </c>
+      <c r="AP4">
+        <v>-0.8710526315789473</v>
+      </c>
+      <c r="AQ4">
+        <v>-13.97590361445783</v>
       </c>
     </row>
   </sheetData>
